--- a/doc_testbed/Target_v13_testballoons.xlsx
+++ b/doc_testbed/Target_v13_testballoons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hans\Documents\GitHub\shepherd_v2_planning\doc_testbed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99DF5E1-47EE-445B-9F81-C3E72CE28110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1992FE59-331E-453A-B38D-9B83A2CE5521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="1836" windowWidth="15156" windowHeight="23088" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
+    <workbookView xWindow="12384" yWindow="1848" windowWidth="19632" windowHeight="22932" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>Target</t>
   </si>
@@ -124,6 +124,27 @@
   </si>
   <si>
     <t>darmstadt</t>
+  </si>
+  <si>
+    <t>GPIO 2 - nRF Side - no 240R / Open Line</t>
+  </si>
+  <si>
+    <t>GPIO 11 - nRF Side - 10 Ohm GND</t>
+  </si>
+  <si>
+    <t>GPIO 13 - nRF Side - 510 Ohm VCC</t>
+  </si>
+  <si>
+    <t>GPIO 5 &amp; 15 - nRF Side - 10 Ohm connected / Short</t>
+  </si>
+  <si>
+    <t>GPIO 8 &amp; 9 - MidPoint - 330 Ohm Connect</t>
+  </si>
+  <si>
+    <t>GPIO 4 &amp; 10 - MidPoint - Diode from 4 to 10</t>
+  </si>
+  <si>
+    <t>added faults</t>
   </si>
 </sst>
 </file>
@@ -179,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -198,6 +219,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,8 +836,12 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -823,8 +851,12 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -835,7 +867,9 @@
     </row>
     <row r="13" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="1"/>
+      <c r="B13" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -846,7 +880,9 @@
     </row>
     <row r="14" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -857,7 +893,9 @@
     </row>
     <row r="15" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -868,7 +906,9 @@
     </row>
     <row r="16" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -879,7 +919,7 @@
     </row>
     <row r="17" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
